--- a/BOM/TDS_Meter/JLCPCB-BOM.xlsx
+++ b/BOM/TDS_Meter/JLCPCB-BOM.xlsx
@@ -93,9 +93,6 @@
     <t>LCSC Part Number</t>
   </si>
   <si>
-    <t>C492401</t>
-  </si>
-  <si>
     <t>C558180</t>
   </si>
   <si>
@@ -109,6 +106,9 @@
   </si>
   <si>
     <t>C128549</t>
+  </si>
+  <si>
+    <t>C492405</t>
   </si>
 </sst>
 </file>
@@ -602,7 +602,7 @@
         <v>17</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -616,7 +616,7 @@
         <v>18</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -630,7 +630,7 @@
         <v>19</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -644,7 +644,7 @@
         <v>20</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -658,7 +658,7 @@
         <v>19</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -672,7 +672,7 @@
         <v>21</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
